--- a/tests/data/ncorf_mammals/S3.xlsx
+++ b/tests/data/ncorf_mammals/S3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,293 @@
       </c>
       <c r="S7" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1_167936685_167936702_+</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>uORF</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>167936685</v>
+      </c>
+      <c r="I8" t="n">
+        <v>167936702</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ENSG00000143164</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>protein_coding</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ENST00000367840</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1_53838293_53838276_-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>uORF</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CTG</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>53838293</v>
+      </c>
+      <c r="I9" t="n">
+        <v>53838276</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ENSG00000058804</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>protein_coding</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ENST00000371429</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>21</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>c1riboseqorf101</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>phase1</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Tier 4</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7_96709845_96709825_-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>uORF</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GTG</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>96709845</v>
+      </c>
+      <c r="I10" t="n">
+        <v>96709825</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ENSG00000127922</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>protein_coding</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ENST00000248566</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6_134530858_134525331_-</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lncORF</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>234</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ATG</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>134530858</v>
+      </c>
+      <c r="I11" t="n">
+        <v>134525331</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ENSG00000232310</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>lncRNA</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ENST00000607531</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>817</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1050</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
